--- a/templates/staff-list-template.xlsx
+++ b/templates/staff-list-template.xlsx
@@ -104,7 +104,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Group (Resident or Middle grade)</t>
+          <t xml:space="preserve">Group (Resident or Senior doctor)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -160,16 +160,16 @@
         </is>
       </c>
       <c r="E2" s="2">
-        <v>46232</v>
+        <v>46239</v>
       </c>
       <c r="F2" s="2">
-        <v>46350</v>
+        <v>46357</v>
       </c>
       <c r="G2">
         <v>9</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -194,16 +194,16 @@
         </is>
       </c>
       <c r="E3" s="2">
-        <v>46232</v>
+        <v>46239</v>
       </c>
       <c r="F3" s="2">
-        <v>46350</v>
+        <v>46357</v>
       </c>
       <c r="G3">
         <v>9</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -228,27 +228,27 @@
         </is>
       </c>
       <c r="E4" s="2">
-        <v>46232</v>
+        <v>46239</v>
       </c>
       <c r="F4" s="2">
         <v>46290</v>
       </c>
       <c r="G4">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">T. Hughes</t>
+          <t xml:space="preserve">K. Ahmed</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2 (on calls NHH)</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -258,31 +258,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">t.hughes@example.nhs.uk</t>
+          <t xml:space="preserve">k.ahmed@example.nhs.uk</t>
         </is>
       </c>
       <c r="E5" s="2">
-        <v>46232</v>
+        <v>46307</v>
       </c>
       <c r="F5" s="2">
-        <v>46350</v>
+        <v>46357</v>
       </c>
       <c r="G5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">S. Malik</t>
+          <t xml:space="preserve">T. Hughes</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMT2</t>
+          <t xml:space="preserve">F2 (on calls NHH)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -292,17 +292,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">s.malik@example.nhs.uk</t>
+          <t xml:space="preserve">t.hughes@example.nhs.uk</t>
         </is>
       </c>
       <c r="E6" s="2">
-        <v>46232</v>
+        <v>46239</v>
       </c>
       <c r="F6" s="2">
-        <v>46413</v>
+        <v>46357</v>
       </c>
       <c r="G6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H6">
         <v>15</v>
@@ -311,12 +311,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">B. Carter</t>
+          <t xml:space="preserve">S. Malik</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMT3</t>
+          <t xml:space="preserve">IMT2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -326,14 +326,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">b.carter@example.nhs.uk</t>
+          <t xml:space="preserve">s.malik@example.nhs.uk</t>
         </is>
       </c>
       <c r="E7" s="2">
-        <v>46232</v>
+        <v>46239</v>
       </c>
       <c r="F7" s="2">
-        <v>46413</v>
+        <v>46420</v>
       </c>
       <c r="G7">
         <v>14</v>
@@ -345,12 +345,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">L. Osei</t>
+          <t xml:space="preserve">B. Carter</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">JCF</t>
+          <t xml:space="preserve">IMT3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -360,79 +360,82 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">l.osei@example.nhs.uk</t>
+          <t xml:space="preserve">b.carter@example.nhs.uk</t>
         </is>
       </c>
       <c r="E8" s="2">
-        <v>46232</v>
+        <v>46239</v>
       </c>
       <c r="F8" s="2">
-        <v>46595</v>
+        <v>46420</v>
       </c>
       <c r="G8">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="H8">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar</t>
+          <t xml:space="preserve">L. Osei</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Middle grade</t>
+          <t xml:space="preserve">JCF</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Middle grade</t>
+          <t xml:space="preserve">Resident</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">omar@example.nhs.uk</t>
+          <t xml:space="preserve">l.osei@example.nhs.uk</t>
         </is>
       </c>
       <c r="E9" s="2">
-        <v>45292</v>
+        <v>46239</v>
+      </c>
+      <c r="F9" s="2">
+        <v>46602</v>
       </c>
       <c r="G9">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hannah</t>
+          <t xml:space="preserve">Omar</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Middle grade</t>
+          <t xml:space="preserve">Registrar ST6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Middle grade</t>
+          <t xml:space="preserve">Senior doctor</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">hannah@example.nhs.uk</t>
+          <t xml:space="preserve">omar@example.nhs.uk</t>
         </is>
       </c>
       <c r="E10" s="2">
         <v>45292</v>
       </c>
       <c r="G10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H10">
         <v>10</v>
@@ -441,29 +444,29 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniel</t>
+          <t xml:space="preserve">Hannah</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Middle grade</t>
+          <t xml:space="preserve">Registrar ST4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Middle grade</t>
+          <t xml:space="preserve">Senior doctor</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">daniel@example.nhs.uk</t>
+          <t xml:space="preserve">hannah@example.nhs.uk</t>
         </is>
       </c>
       <c r="E11" s="2">
         <v>45292</v>
       </c>
       <c r="G11">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H11">
         <v>10</v>
@@ -472,29 +475,29 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zara</t>
+          <t xml:space="preserve">Daniel</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Middle grade</t>
+          <t xml:space="preserve">Specialty doctor</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Middle grade</t>
+          <t xml:space="preserve">Senior doctor</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">zara@example.nhs.uk</t>
+          <t xml:space="preserve">daniel@example.nhs.uk</t>
         </is>
       </c>
       <c r="E12" s="2">
         <v>45292</v>
       </c>
       <c r="G12">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H12">
         <v>10</v>
@@ -503,29 +506,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meera</t>
+          <t xml:space="preserve">Zara</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Middle grade</t>
+          <t xml:space="preserve">Registrar ST5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Middle grade</t>
+          <t xml:space="preserve">Senior doctor</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">meera@example.nhs.uk</t>
+          <t xml:space="preserve">zara@example.nhs.uk</t>
         </is>
       </c>
       <c r="E13" s="2">
         <v>45292</v>
       </c>
       <c r="G13">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H13">
         <v>10</v>
@@ -534,31 +537,62 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yusuf</t>
+          <t xml:space="preserve">Meera</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Middle grade</t>
+          <t xml:space="preserve">Specialty doctor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Middle grade</t>
+          <t xml:space="preserve">Senior doctor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">yusuf@example.nhs.uk</t>
+          <t xml:space="preserve">meera@example.nhs.uk</t>
         </is>
       </c>
       <c r="E14" s="2">
         <v>45292</v>
       </c>
       <c r="G14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yusuf</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senior clinical fellow</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senior doctor</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yusuf@example.nhs.uk</t>
+        </is>
+      </c>
+      <c r="E15" s="2">
+        <v>45292</v>
+      </c>
+      <c r="G15">
+        <v>28</v>
+      </c>
+      <c r="H15">
         <v>10</v>
       </c>
     </row>

--- a/templates/staff-list-template.xlsx
+++ b/templates/staff-list-template.xlsx
@@ -231,10 +231,10 @@
         <v>46239</v>
       </c>
       <c r="F4" s="2">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="H4">
         <v>15</v>
@@ -262,13 +262,13 @@
         </is>
       </c>
       <c r="E5" s="2">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="F5" s="2">
         <v>46357</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="H5">
         <v>15</v>

--- a/templates/staff-list-template.xlsx
+++ b/templates/staff-list-template.xlsx
@@ -413,74 +413,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar</t>
+          <t xml:space="preserve">New F1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registrar ST6</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Senior doctor</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">omar@example.nhs.uk</t>
+          <t xml:space="preserve">Resident</t>
         </is>
       </c>
       <c r="E10" s="2">
-        <v>45292</v>
+        <v>46358</v>
+      </c>
+      <c r="F10" s="2">
+        <v>46483</v>
       </c>
       <c r="G10">
-        <v>33</v>
+        <v>9.5</v>
       </c>
       <c r="H10">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hannah</t>
+          <t xml:space="preserve">New F2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registrar ST4</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Senior doctor</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hannah@example.nhs.uk</t>
+          <t xml:space="preserve">Resident</t>
         </is>
       </c>
       <c r="E11" s="2">
-        <v>45292</v>
+        <v>46358</v>
+      </c>
+      <c r="F11" s="2">
+        <v>46483</v>
       </c>
       <c r="G11">
-        <v>33</v>
+        <v>9.5</v>
       </c>
       <c r="H11">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniel</t>
+          <t xml:space="preserve">Omar</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Specialty doctor</t>
+          <t xml:space="preserve">Registrar ST6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -490,14 +486,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">daniel@example.nhs.uk</t>
+          <t xml:space="preserve">omar@example.nhs.uk</t>
         </is>
       </c>
       <c r="E12" s="2">
         <v>45292</v>
       </c>
       <c r="G12">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H12">
         <v>10</v>
@@ -506,12 +502,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zara</t>
+          <t xml:space="preserve">Hannah</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registrar ST5</t>
+          <t xml:space="preserve">Registrar ST4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -521,7 +517,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">zara@example.nhs.uk</t>
+          <t xml:space="preserve">hannah@example.nhs.uk</t>
         </is>
       </c>
       <c r="E13" s="2">
@@ -537,7 +533,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meera</t>
+          <t xml:space="preserve">Daniel</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -552,7 +548,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">meera@example.nhs.uk</t>
+          <t xml:space="preserve">daniel@example.nhs.uk</t>
         </is>
       </c>
       <c r="E14" s="2">
@@ -568,12 +564,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yusuf</t>
+          <t xml:space="preserve">Zara</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Senior clinical fellow</t>
+          <t xml:space="preserve">Registrar ST5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -583,16 +579,78 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">yusuf@example.nhs.uk</t>
+          <t xml:space="preserve">zara@example.nhs.uk</t>
         </is>
       </c>
       <c r="E15" s="2">
         <v>45292</v>
       </c>
       <c r="G15">
+        <v>33</v>
+      </c>
+      <c r="H15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meera</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Specialty doctor</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senior doctor</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">meera@example.nhs.uk</t>
+        </is>
+      </c>
+      <c r="E16" s="2">
+        <v>45292</v>
+      </c>
+      <c r="G16">
+        <v>29</v>
+      </c>
+      <c r="H16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yusuf</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senior clinical fellow</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senior doctor</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yusuf@example.nhs.uk</t>
+        </is>
+      </c>
+      <c r="E17" s="2">
+        <v>45292</v>
+      </c>
+      <c r="G17">
         <v>28</v>
       </c>
-      <c r="H15">
+      <c r="H17">
         <v>10</v>
       </c>
     </row>
